--- a/AAII_Financials/Quarterly/MTSUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTSUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
   <si>
     <t>MTSUY</t>
   </si>
@@ -656,65 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -751,8 +754,11 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -789,8 +795,11 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -827,8 +836,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -843,8 +855,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -881,8 +894,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -919,8 +935,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -957,8 +976,11 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -995,8 +1017,11 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1008,8 +1033,9 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1046,8 +1072,11 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1084,8 +1113,11 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1100,8 +1132,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1138,8 +1171,11 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1176,8 +1212,11 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1214,8 +1253,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1252,8 +1294,11 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1290,8 +1335,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1328,8 +1376,11 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1366,8 +1417,11 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1404,8 +1458,11 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1442,8 +1499,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1480,8 +1540,11 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1518,8 +1581,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1556,8 +1622,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1594,8 +1663,11 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1632,8 +1704,11 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1670,8 +1745,11 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1708,51 +1786,57 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1767,8 +1851,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1783,350 +1868,378 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11581200</v>
+      </c>
+      <c r="E41" s="3">
         <v>9321100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10261400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8054500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8274400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10271400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11712600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9889900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10271400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11516700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11712600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11633000</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>108600</v>
+      </c>
+      <c r="E42" s="3">
         <v>1286900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>725000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>735000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>657800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>683900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1033700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>808200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>683900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>925600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1033700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1135100</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26328500</v>
+      </c>
+      <c r="E43" s="3">
         <v>27496900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>27832400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>25260100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>28051800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>27817500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>31047500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>30394400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>27817500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>27884000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>31047500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>33572100</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>13059900</v>
+      </c>
+      <c r="E44" s="3">
         <v>11891000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>11776400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>12024900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>11399400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>12375300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>13325300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12690500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12375300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12562900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13325300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>13562600</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12892600</v>
+      </c>
+      <c r="E45" s="3">
         <v>8343400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7852100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>27273500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>28813900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9196000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11405900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13871700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9196000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9403700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11405900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12032500</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>63970700</v>
+      </c>
+      <c r="E46" s="3">
         <v>58339300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>58447300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>73348000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>77197400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>60344200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>68525000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>67654700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>60344200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>62292900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>68525000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>71935300</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>46958800</v>
+      </c>
+      <c r="E47" s="3">
         <v>48964200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>47594200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>42229400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>41755000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>40996100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>43166900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>40702500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>40996100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>40526300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>43166900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>44248000</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26541100</v>
+      </c>
+      <c r="E48" s="3">
         <v>24592200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23786500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20889400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20817700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32748500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>34470700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>31546000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>32748500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33161000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34470700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34246400</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5744300</v>
+      </c>
+      <c r="E49" s="3">
         <v>5359500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5067900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4996900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4911500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8315300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9082700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8524700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8315300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8590500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9082700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9223800</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2163,8 +2276,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2201,46 +2317,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3419300</v>
+      </c>
+      <c r="E52" s="3">
         <v>2875700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2775900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2797300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3038700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3004500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3654700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4419100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3004500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3248900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3654700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3762500</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2277,46 +2399,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>151892700</v>
+      </c>
+      <c r="E54" s="3">
         <v>146406000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>143548500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>151498400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>155099500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>153264600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>166605200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>160441700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>153264600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>155972600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>166605200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>171177800</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2331,8 +2459,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2347,236 +2476,255 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19362200</v>
+      </c>
+      <c r="E57" s="3">
         <v>18416900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>19230300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17891800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18835100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23568800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>25343500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>24830500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>23568800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>22803800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>25343500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>28131500</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10907500</v>
+      </c>
+      <c r="E58" s="3">
         <v>11922000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9717700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12752800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12201300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11708700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12487200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12421400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11708700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12184700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12487200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>14358000</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15062100</v>
+      </c>
+      <c r="E59" s="3">
         <v>9753800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10338100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20918000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>22727700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9239300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12530200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15518200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9239300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10751700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12530200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13279800</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>45331700</v>
+      </c>
+      <c r="E60" s="3">
         <v>40092700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>39286100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>51562600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>53764000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>44516800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>50360900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>52770100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>44516800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>45740200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>50360900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>55769400</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>30021100</v>
+      </c>
+      <c r="E61" s="3">
         <v>28294600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>25937500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>24092100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>25394800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>32463600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>36842300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>34755300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>32463600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>34067800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>36842300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>36288500</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4572900</v>
+      </c>
+      <c r="E62" s="3">
         <v>3790400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3703500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3251900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3248600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4374400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4803700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5785500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4374400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4497500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4803700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5300900</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2613,8 +2761,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2651,8 +2802,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2689,46 +2843,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>87425700</v>
+      </c>
+      <c r="E66" s="3">
         <v>79250700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>75739100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>85217800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>88359000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>87206100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>98007000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>98915700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>87206100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>89951700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>98007000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>103382400</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2743,8 +2903,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2781,8 +2942,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2819,8 +2983,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2857,8 +3024,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2895,46 +3065,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>43734700</v>
+      </c>
+      <c r="E72" s="3">
         <v>45036100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>44324700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>41433600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>42656800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>41976300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>45465300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>39870000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>41976300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>42300500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>45465300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>44680800</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2971,8 +3147,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3009,8 +3188,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3047,46 +3229,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>59372800</v>
+      </c>
+      <c r="E76" s="3">
         <v>61730200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>62563200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>59430700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>59792200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>58768200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>60674000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>54571900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>58768200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>58606400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>60674000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>60098500</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3123,51 +3311,57 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3204,8 +3398,11 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3220,46 +3417,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>445800</v>
+      </c>
+      <c r="E83" s="3">
         <v>1003300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>546400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>981300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1035300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>442700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1201200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1215200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>981300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1035300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>442700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1182000</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3296,8 +3497,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3334,8 +3538,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3372,8 +3579,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3410,8 +3620,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3448,46 +3661,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5983400</v>
+      </c>
+      <c r="E89" s="3">
         <v>749800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2566000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2101200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2263100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1406500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3799600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2330600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1406500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3365800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3799600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2788400</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3502,46 +3721,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-544500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-544400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-570300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-609000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-852600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-819900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-895500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-814000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-819900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-830600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-895500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-917500</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3578,8 +3801,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3616,46 +3842,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-245300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1313200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>355100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>891600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-948000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-197100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-279400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-683100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-197100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>438300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-279400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-908500</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3670,23 +3902,24 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3">
         <v>1378600</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>891600</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
@@ -3700,16 +3933,19 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>1017900</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>850600</v>
       </c>
     </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3746,8 +3982,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3784,8 +4023,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3822,118 +4064,130 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3900200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-741000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1738500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2620900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2512900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2154400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3327300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4304800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2154400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3289100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3327300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-825000</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>55900</v>
+      </c>
+      <c r="E101" s="3">
         <v>67900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-20500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-16000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>415100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>214400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-19400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>68300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-16000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>415100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>214400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>98900</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2008900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1329500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1227800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>649500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1141900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-877000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>172400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2673300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-877000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>748000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>172400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>782100</v>
       </c>
     </row>
